--- a/pensum/ok04/OK04_Regnskapsanalyse_Regneark_Nokkeltall.xlsx
+++ b/pensum/ok04/OK04_Regnskapsanalyse_Regneark_Nokkeltall.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="410">
   <si>
     <t xml:space="preserve">Hvorfor får eierne 48,7 prosent? Den enkle versjonen</t>
   </si>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">Nøkkeltall</t>
   </si>
   <si>
-    <t xml:space="preserve">De sju nøkkeltallene regnet av Nordlys-arket, med bransjetall og normtall ved siden av. Under dem de fem effektivitetstallene, Du Pont-modellen og de to vanligste regnefeilene.</t>
+    <t xml:space="preserve">De sju nøkkeltallene regnet av Nordlys-arket, med bransjetall og normtall ved siden av. Under dem de fem effektivitetstallene, resultatgraden og de to vanligste regnefeilene.</t>
   </si>
   <si>
     <t xml:space="preserve">Din bedrift</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">leverandører, lagringstid, varelagerets og kapitalens omløpshastighet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Du Pont: totalkapitalrentabilitet = resultatgrad × kapitalens omløpshastighet.</t>
+    <t xml:space="preserve">Kredittidene og lagringstiden regnes med 360 dager i året, slik boka gjør.</t>
   </si>
   <si>
     <t xml:space="preserve">Tallene som ligger inne er et eksempel fra en elektrobedrift. Bytt dem ut med dine egne — alle formler følger med.</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">2 · Kapitalavkastningen</t>
   </si>
   <si>
-    <t xml:space="preserve">Se hvordan gjennomsnittstallene kommer fram i «Nordlys» radene 45 til 51. Les av C7, C8 og C15 i «Nøkkeltall», og de to regnefeilene i C47 og C48. Du Pont-blokka i radene 38 til 44 viser hvorfor TKR er som den er.</t>
+    <t xml:space="preserve">Se hvordan gjennomsnittstallene kommer fram i «Nordlys» radene 45 til 51. Les av C7, C8 og C15 i «Nøkkeltall», og de to regnefeilene i C41 og C42.</t>
   </si>
   <si>
     <t xml:space="preserve">3 · Betalingsevne og soliditet</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">Fem unntak: kontrollen på egenkapitalandelen i arket «Nøkkeltall», den første i «Les og tolk», de to første i scenario A og den første i scenario C skal vise AVVIK med tallene som ligger inne. Der er avviket selve svaret — Nordlys ligger under bransjen, søker B ser mest lønnsom ut, et utbytte gjør bedriften svakere samtidig som ett nøkkeltall ser bedre ut, og de to bedriftene til salgs koster praktisk talt det samme.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kontroller i arbeidsboka: Nordlys B43, Nordlys B54, Nordlys B55, Nøkkeltall B51, Nøkkeltall B52, Nøkkeltall B53, Nøkkeltall B54, Nøkkeltall B55, Nøkkeltall B56, Nøkkeltall B58, Fra kapittel 3 B33, Fra kapittel 3 B34, Din bedrift B49, Din bedrift B50, Les og tolk B24, Les og tolk B26, Les og tolk B27, Scenario B22, Scenario B24, Scenario B26, Scenario B44, Scenario B45, Scenario B80, Scenario B82, Scenario B83</t>
+    <t xml:space="preserve">Kontroller i arbeidsboka: Nordlys B43, Nordlys B54, Nordlys B55, Nøkkeltall B45, Nøkkeltall B46, Nøkkeltall B47, Nøkkeltall B48, Nøkkeltall B50, Fra kapittel 3 B33, Fra kapittel 3 B34, Din bedrift B49, Din bedrift B50, Les og tolk B24, Les og tolk B26, Les og tolk B27, Scenario B22, Scenario B24, Scenario B26, Scenario B44, Scenario B45, Scenario B80, Scenario B82, Scenario B83</t>
   </si>
   <si>
     <t xml:space="preserve">Slik henger kapitlet sammen med resten</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">Kredittid kunder</t>
   </si>
   <si>
-    <t xml:space="preserve">Kundefordringer × 365 / salgsinntekt inkl. mva.</t>
+    <t xml:space="preserve">Kundefordringer × 360 / salgsinntekt inkl. mva.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvor mange dager det i snitt går fra du sender fakturaen til pengene er på konto.</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">Kredittid leverandører</t>
   </si>
   <si>
-    <t xml:space="preserve">Leverandørgjeld × 365 / varekjøp inkl. mva.</t>
+    <t xml:space="preserve">Leverandørgjeld × 360 / varekjøp inkl. mva.</t>
   </si>
   <si>
     <t xml:space="preserve">Hvor mange dager du i snitt bruker på å betale grossisten. Dette er gratis finansiering så lenge du holder fristen.</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">Gjennomsnittlig lagringstid</t>
   </si>
   <si>
-    <t xml:space="preserve">365 / varelagerets omløpshastighet</t>
+    <t xml:space="preserve">360 / varelagerets omløpshastighet</t>
   </si>
   <si>
     <t xml:space="preserve">Hvor lenge en kveilrull i snitt står på hylla før den er montert og fakturert.</t>
@@ -734,39 +734,18 @@
     <t xml:space="preserve">Uten én krone i økt omsetning. Fakturer samme dag jobben er ferdig, og purr.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 · Du Pont — de to veiene til samme lønnsomhet</t>
+    <t xml:space="preserve">4 · Resultatgrad</t>
   </si>
   <si>
     <t xml:space="preserve">Resultatgrad</t>
   </si>
   <si>
+    <t xml:space="preserve">(Resultat før skatt + rentekostnader) / salgsinntekt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hvor mye som blir igjen av hver krone du fakturerer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hvor mange kroner i omsetning hver krone i bedriften drar inn på et år.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">= Resultatgrad × omløpshastighet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dette ER totalkapitalrentabiliteten. Du Pont er ingen ny formel — den viser de to knappene du kan skru på.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To bedrifter, samme lønnsomhet, helt ulik drift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marginbedriften — få og store jobber, høyt påslag, mye kapital bundet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dobbel margin, halv omløpshastighet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumbedriften — mange små serviceoppdrag, lavt påslag, lite bundet kapital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Halv margin, dobbel omløpshastighet. Begge ender på det samme.</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 · De to vanligste regnefeilene</t>
   </si>
   <si>
@@ -789,12 +768,6 @@
   </si>
   <si>
     <t xml:space="preserve">Stemmer gjeldsgraden med egenkapitalandelen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Går Du Pont opp mot totalkapitalrentabiliteten?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gir de to Du Pont-bedriftene samme lønnsomhet?</t>
   </si>
   <si>
     <t xml:space="preserve">Ligger egenkapitalandelen på bransjenivå?</t>
@@ -1493,12 +1466,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1506,11 +1483,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1518,7 +1495,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1526,11 +1503,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1538,11 +1515,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1554,31 +1531,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1586,63 +1563,63 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1910,207 +1887,207 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>1190000</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>210000</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>9800000</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>2446000</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="9" t="n">
         <f aca="false">B5+B6</f>
         <v>1400000</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <f aca="false">B11/B7</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <f aca="false">B7-B8</f>
         <v>7354000</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="10" t="n">
         <f aca="false">B6/B13</f>
         <v>0.0285558879521349</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <f aca="false">B5/B8</f>
         <v>0.486508585445626</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <f aca="false">(B12-B14)*100</f>
         <v>11.4301254905008</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="str">
+      <c r="A20" s="14" t="str">
         <f aca="false">"Eierne får "&amp;TEXT(B16,"0.0 %")&amp;" på pengene sine, mens hele kapitalen tjener "&amp;TEXT(B12,"0.0 %")&amp;". Forskjellen kommer av at lånet koster "&amp;TEXT(B14,"0.0 %")&amp;" og egenkapitalen er liten."</f>
         <v>Eierne får 48.7 % på pengene sine, mens hele kapitalen tjener 14.3 %. Forskjellen kommer av at lånet koster 2.9 % og egenkapitalen er liten.</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2139,344 +2116,344 @@
   <dimension ref="A1:C57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="20" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="23" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="20" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="18" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2499,456 +2476,456 @@
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>22400000</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>7990000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>400000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="25" t="n">
         <f aca="false">B6+B7</f>
         <v>8390000</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">B5-B8</f>
         <v>14010000</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <v>10660000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>620000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>1386000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <f aca="false">B8+B10+B11+B12</f>
         <v>21056000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <f aca="false">B5-B13</f>
         <v>1344000</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="24" t="n">
         <v>56000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>210000</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <f aca="false">B14+B15-B16</f>
         <v>1190000</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="24" t="n">
         <v>262000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="26" t="n">
         <f aca="false">B17-B18</f>
         <v>928000</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="20" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="24" t="n">
         <v>1200000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="24" t="n">
         <v>2400000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="25" t="n">
         <f aca="false">B22+B23</f>
         <v>3600000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <v>1400000</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="20" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="24" t="n">
         <v>4200000</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="20" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="24" t="n">
         <v>1000000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <f aca="false">B25+B26+B27</f>
         <v>6600000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <f aca="false">B24+B28</f>
         <v>10200000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="23" t="n">
+      <c r="B32" s="24" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="24" t="n">
         <v>2610000</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="25" t="n">
+      <c r="B34" s="26" t="n">
         <f aca="false">B32+B33</f>
         <v>2910000</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="24" t="n">
         <v>2800000</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="24" t="n">
         <v>2100000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="24" t="n">
         <v>1200000</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="23" t="n">
+      <c r="B38" s="24" t="n">
         <v>890000</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="23" t="n">
+      <c r="B39" s="24" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="25" t="n">
+      <c r="B40" s="26" t="n">
         <f aca="false">B36+B37+B38+B39</f>
         <v>4490000</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B41" s="24" t="n">
+      <c r="B41" s="25" t="n">
         <f aca="false">B35+B40</f>
         <v>7290000</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="26" t="n">
         <f aca="false">B34+B41</f>
         <v>10200000</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="26" t="str">
+      <c r="B43" s="27" t="str">
         <f aca="false">IF(B42=B29,"OK — de to sidene er like store","AVVIK: balansen går ikke opp")</f>
         <v>OK — de to sidene er like store</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="18" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B46" s="23" t="n">
+      <c r="B46" s="24" t="n">
         <v>9400000</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="20" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B47" s="24" t="n">
+      <c r="B47" s="25" t="n">
         <f aca="false">B34-B19</f>
         <v>1982000</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="20" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="24" t="n">
+      <c r="B48" s="25" t="n">
         <f aca="false">B46-B47</f>
         <v>7418000</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="B49" s="25" t="n">
+      <c r="B49" s="26" t="n">
         <f aca="false">(B46+B29)/2</f>
         <v>9800000</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="20" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B50" s="25" t="n">
+      <c r="B50" s="26" t="n">
         <f aca="false">(B47+B34)/2</f>
         <v>2446000</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="B51" s="25" t="n">
+      <c r="B51" s="26" t="n">
         <f aca="false">(B48+B41)/2</f>
         <v>7354000</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B54" s="26" t="str">
+      <c r="B54" s="27" t="str">
         <f aca="false">IF(ABS(B50+B51-B49)&lt;1,"OK — gjennomsnittlig egenkapital pluss gjennomsnittlig gjeld er lik gjennomsnittlig totalkapital","AVVIK: snittene henger ikke sammen")</f>
         <v>OK — gjennomsnittlig egenkapital pluss gjennomsnittlig gjeld er lik gjennomsnittlig totalkapital</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="26" t="str">
+      <c r="B55" s="27" t="str">
         <f aca="false">IF(B47&gt;0,"OK — bedriften hadde egenkapital også ved inngangen til året","AVVIK: negativ inngående egenkapital gjør egenkapitalrentabiliteten meningsløs")</f>
         <v>OK — bedriften hadde egenkapital også ved inngangen til året</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2986,656 +2963,582 @@
   <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <f aca="false">Nordlys!B14/Nordlys!B5</f>
         <v>0.06</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>0.075</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="21" t="str">
         <f aca="false">IF(C6&gt;=D6,"Over normen","Under normen")</f>
         <v>Under normen</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="20" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <f aca="false">(Nordlys!B17+Nordlys!B16)/Nordlys!B49</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="29" t="n">
         <v>0.146</v>
       </c>
-      <c r="E7" s="20" t="str">
+      <c r="E7" s="21" t="str">
         <f aca="false">IF(C7&gt;=D7,"Over normen","Under normen")</f>
         <v>Under normen</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <f aca="false">Nordlys!B17/Nordlys!B50</f>
         <v>0.486508585445626</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="20" t="str">
+      <c r="E8" s="21" t="str">
         <f aca="false">IF(C8&gt;=D8,"Over normen","Under normen")</f>
         <v>Over normen</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <f aca="false">Nordlys!B28/Nordlys!B40</f>
         <v>1.46993318485523</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="20" t="str">
+      <c r="E9" s="21" t="str">
         <f aca="false">IF(C9&gt;=D9,"Over normen","Under normen")</f>
         <v>Under normen</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="20" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <f aca="false">(Nordlys!B28-Nordlys!B25)/Nordlys!B40</f>
         <v>1.15812917594655</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="20" t="str">
+      <c r="E10" s="21" t="str">
         <f aca="false">IF(C10&gt;=D10,"Over normen","Under normen")</f>
         <v>Over normen</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <f aca="false">Nordlys!B34/Nordlys!B29</f>
         <v>0.285294117647059</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="29" t="n">
         <v>0.362</v>
       </c>
-      <c r="E11" s="20" t="str">
+      <c r="E11" s="21" t="str">
         <f aca="false">IF(C11&gt;=D11,"Over normen","Under normen")</f>
         <v>Under normen</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="30" t="n">
         <f aca="false">Nordlys!B41/Nordlys!B34</f>
         <v>2.50515463917526</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="20" t="str">
+      <c r="E12" s="21" t="str">
         <f aca="false">IF(C12&lt;=D12,"Innenfor","Over grensen")</f>
         <v>Innenfor</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="32" t="n">
         <f aca="false">Nordlys!B16/Nordlys!B51</f>
         <v>0.0285558879521349</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">(C7-C15)*100</f>
         <v>11.4301254905008</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="33" t="n">
         <f aca="false">C8/C7</f>
         <v>3.40556009811938</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="34" t="n">
         <f aca="false">Nordlys!B28-Nordlys!B40</f>
         <v>2110000</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="32" t="n">
         <f aca="false">Nordlys!B9/Nordlys!B8</f>
         <v>1.66984505363528</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="20" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="29" t="n">
         <v>0.25</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="20" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="C23" s="33" t="n">
+      <c r="C23" s="34" t="n">
         <f aca="false">Nordlys!B5*(1+B22)</f>
         <v>28000000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="34" t="n">
         <f aca="false">Nordlys!B8*(1+B22)</f>
         <v>10487500</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="20" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22" t="s">
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="C27" s="29" t="n">
-        <f aca="false">Nordlys!B26*365/C23</f>
-        <v>54.75</v>
-      </c>
-      <c r="F27" s="19" t="s">
+      <c r="C27" s="30" t="n">
+        <f aca="false">Nordlys!B26*360/C23</f>
+        <v>54</v>
+      </c>
+      <c r="F27" s="20" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="29" t="n">
-        <f aca="false">Nordlys!B36*365/C24</f>
-        <v>73.0870083432658</v>
-      </c>
-      <c r="F28" s="19" t="s">
+      <c r="C28" s="30" t="n">
+        <f aca="false">Nordlys!B36*360/C24</f>
+        <v>72.0858164481526</v>
+      </c>
+      <c r="F28" s="20" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="30" t="n">
         <f aca="false">Nordlys!B8/Nordlys!B25</f>
         <v>5.99285714285714</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="20" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="29" t="n">
-        <f aca="false">365/C29</f>
-        <v>60.9058402860548</v>
-      </c>
-      <c r="F30" s="19" t="s">
+      <c r="C30" s="30" t="n">
+        <f aca="false">360/C29</f>
+        <v>60.0715137067938</v>
+      </c>
+      <c r="F30" s="20" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <f aca="false">Nordlys!B5/Nordlys!B49</f>
         <v>2.28571428571429</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="20" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="B33" s="34" t="n">
+      <c r="B33" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="20" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="C34" s="32" t="n">
+      <c r="C34" s="33" t="n">
         <f aca="false">C27-B33</f>
-        <v>34.75</v>
-      </c>
-      <c r="F34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="20" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="33" t="n">
-        <f aca="false">C23*10/365</f>
-        <v>767123.287671233</v>
-      </c>
-      <c r="F35" s="19" t="s">
+      <c r="C35" s="34" t="n">
+        <f aca="false">C23*10/360</f>
+        <v>777777.777777778</v>
+      </c>
+      <c r="F35" s="20" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="C38" s="31" t="n">
+      <c r="B38" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="32" t="n">
         <f aca="false">(Nordlys!B17+Nordlys!B16)/Nordlys!B5</f>
         <v>0.0625</v>
       </c>
-      <c r="F38" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="C39" s="32" t="n">
-        <f aca="false">C31</f>
-        <v>2.28571428571429</v>
-      </c>
-      <c r="F39" s="19" t="s">
+      <c r="F38" s="20" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="C40" s="27" t="n">
-        <f aca="false">C38*C39</f>
-        <v>0.142857142857143</v>
-      </c>
-      <c r="F40" s="19" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C43" s="31" t="n">
-        <f aca="false">C38*2*(C39/2)</f>
-        <v>0.142857142857143</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C44" s="31" t="n">
-        <f aca="false">(C38/2)*C39*2</f>
-        <v>0.142857142857143</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="31" t="n">
+      <c r="C41" s="32" t="n">
         <f aca="false">Nordlys!B17/Nordlys!B49</f>
         <v>0.121428571428571</v>
       </c>
-      <c r="F47" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="C48" s="31" t="n">
+      <c r="F41" s="20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="32" t="n">
         <f aca="false">Nordlys!B19/Nordlys!B50</f>
         <v>0.379394930498774</v>
       </c>
-      <c r="F48" s="19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
+      <c r="F42" s="20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="B51" s="26" t="str">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="B45" s="27" t="str">
         <f aca="false">IF(C7&gt;C15,"OK — den lånte kapitalen tjener mer enn den koster, og differansen tilfaller eierne","AVVIK: lånene spiser egenkapitalen — da virker gjeldsgraden mot eierne i stedet for for dem")</f>
         <v>OK — den lånte kapitalen tjener mer enn den koster, og differansen tilfaller eierne</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="B52" s="26" t="str">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B46" s="27" t="str">
         <f aca="false">IF(C10&lt;=C9,"OK — grad 2 er alltid lavest, fordi varelageret er trukket ut","AVVIK: varelageret kan ikke være negativt")</f>
         <v>OK — grad 2 er alltid lavest, fordi varelageret er trukket ut</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="B53" s="26" t="str">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B47" s="27" t="str">
         <f aca="false">IF(ABS(C12-(1-C11)/C11)&lt;0.001,"OK — gjeldsgraden og egenkapitalandelen sier det samme to ganger. Den ene er den andre snudd på hodet","AVVIK: de to henger ikke sammen")</f>
         <v>OK — gjeldsgraden og egenkapitalandelen sier det samme to ganger. Den ene er den andre snudd på hodet</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="B54" s="26" t="str">
-        <f aca="false">IF(ABS(C40-C7)&lt;0.0001,"OK — resultatgrad ganget med kapitalens omløpshastighet gir nøyaktig totalkapitalrentabiliteten","AVVIK: da er en av de tre tallene regnet av feil grunnlag")</f>
-        <v>OK — resultatgrad ganget med kapitalens omløpshastighet gir nøyaktig totalkapitalrentabiliteten</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="B55" s="26" t="str">
-        <f aca="false">IF(ABS(C43-C44)&lt;0.0001,"OK — samme totalkapitalrentabilitet, helt ulik vei dit. Ingen av dem er den riktige, men du må vite hvilken du driver","AVVIK: da viser eksempelet ikke lenger to veier til SAMME lønnsomhet")</f>
-        <v>OK — samme totalkapitalrentabilitet, helt ulik vei dit. Ingen av dem er den riktige, men du må vite hvilken du driver</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="B56" s="26" t="str">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" s="27" t="str">
         <f aca="false">IF(C11&gt;=D11,"OK — egenkapitalandelen er på eller over bransjens nivå","AVVIK: egenkapitalandelen ligger under bransjen. Det er det første banken ser")</f>
         <v>AVVIK: egenkapitalandelen ligger under bransjen. Det er det første banken ser</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="B58" s="26" t="str">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B50" s="27" t="str">
         <f aca="false">IF(C30+C27-C28&gt;0,"OK — og det er nettopp derfor kassekreditten brukes: fra kabelen kjøpes til kunden betaler går det "&amp;TEXT(C30+C27,"0")&amp;" dager, grossisten finansierer "&amp;TEXT(C28,"0")&amp;" av dem, og de siste "&amp;TEXT(C30+C27-C28,"0")&amp;" må Nordlys finansiere selv","AVVIK: da finansierer leverandørene hele driften, og kassekreditten skulle vært unødvendig")</f>
-        <v>OK — og det er nettopp derfor kassekreditten brukes: fra kabelen kjøpes til kunden betaler går det 116 dager, grossisten finansierer 73 av dem, og de siste 43 må Nordlys finansiere selv</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="21" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="16" t="s">
-        <v>262</v>
-      </c>
-    </row>
+        <v>OK — og det er nettopp derfor kassekreditten brukes: fra kabelen kjøpes til kunden betaler går det 114 dager, grossisten finansierer 72 av dem, og de siste 42 må Nordlys finansiere selv</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="22" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="B51">
+  <conditionalFormatting sqref="B45">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(B51,5)="AVVIK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(B52,5)="AVVIK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
+  <conditionalFormatting sqref="B47">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(B53,5)="AVVIK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(B54,5)="AVVIK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(B55,5)="AVVIK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(B56,5)="AVVIK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="B50">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>LEFT(B58,5)="AVVIK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3657,294 +3560,294 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>265</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B6" s="25" t="n">
+      <c r="A5" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <f aca="false">Nordlys!B5</f>
         <v>22400000</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="25" t="n">
+      <c r="C6" s="20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <f aca="false">Nordlys!B14</f>
         <v>1344000</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="25" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <f aca="false">Nordlys!B17</f>
         <v>1190000</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="C8" s="20" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">Nordlys!B16</f>
         <v>210000</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="B10" s="25" t="n">
+      <c r="C9" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">Nordlys!B29</f>
         <v>10200000</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="B11" s="25" t="n">
+      <c r="C10" s="20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <f aca="false">Nordlys!B34</f>
         <v>2910000</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="B12" s="25" t="n">
+      <c r="C11" s="20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <f aca="false">Nordlys!B28</f>
         <v>6600000</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="C12" s="20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <f aca="false">Nordlys!B25</f>
         <v>1400000</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="B14" s="25" t="n">
+      <c r="C13" s="20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <f aca="false">Nordlys!B40</f>
         <v>4490000</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B17" s="33" t="n">
+      <c r="C14" s="20" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B17" s="34" t="n">
         <f aca="false">Nordlys!B46</f>
         <v>9400000</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="C17" s="20" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <f aca="false">Nøkkeltall!C11</f>
         <v>0.285294117647059</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+      <c r="C22" s="20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <f aca="false">Nøkkeltall!C12</f>
         <v>2.50515463917526</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <f aca="false">Nøkkeltall!C9</f>
         <v>1.46993318485523</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <f aca="false">Nøkkeltall!C10</f>
         <v>1.15812917594655</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="32" t="n">
         <f aca="false">Nøkkeltall!C6</f>
         <v>0.06</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+      <c r="C28" s="20" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="32" t="n">
         <f aca="false">Nøkkeltall!C7</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+      <c r="C29" s="20" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B30" s="31" t="n">
+      <c r="B30" s="32" t="n">
         <f aca="false">Nøkkeltall!C8</f>
         <v>0.486508585445626</v>
       </c>
-      <c r="C30" s="19" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+      <c r="C30" s="20" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="B33" s="26" t="str">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B33" s="27" t="str">
         <f aca="false">IF(AND(B6=Nordlys!B5,B10=Nordlys!B29,B11=Nordlys!B34,B14=Nordlys!B40),"OK — alle er formler. Endrer du en post i arket Nordlys, endrer nøkkeltallet seg overalt","AVVIK: en av koblingene er brutt")</f>
         <v>OK — alle er formler. Endrer du en post i arket Nordlys, endrer nøkkeltallet seg overalt</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="B34" s="26" t="str">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="B34" s="27" t="str">
         <f aca="false">IF(ABS(B10-Nordlys!B24-B12)&lt;1,"OK — sum eiendeler er anleggsmidler pluss omløpsmidler","AVVIK: balansetallene henger ikke sammen")</f>
         <v>OK — sum eiendeler er anleggsmidler pluss omløpsmidler</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
-        <v>300</v>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3976,448 +3879,448 @@
   <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="E4" s="34" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="35" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="23" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <v>22400000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="24" t="n">
         <v>8390000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>10660000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <v>620000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>1386000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>56000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>210000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>262000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <f aca="false">B7-B8-B9-B10-B11</f>
         <v>1344000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="26" t="n">
         <f aca="false">B15+B12-B13</f>
         <v>1190000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <f aca="false">B16-B14</f>
         <v>928000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="24" t="n">
         <v>3600000</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="24" t="n">
         <v>1400000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="24" t="n">
         <v>4200000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="B23" s="23" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" s="24" t="n">
         <v>1000000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="B24" s="23" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="B24" s="24" t="n">
         <v>2910000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="B25" s="23" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="B25" s="24" t="n">
         <v>2800000</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="B26" s="23" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B26" s="24" t="n">
         <v>4490000</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="24" t="n">
         <v>9400000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <f aca="false">B21+B22+B23</f>
         <v>6600000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <f aca="false">B20+B28</f>
         <v>10200000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="B30" s="25" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="B30" s="26" t="n">
         <f aca="false">B25+B26</f>
         <v>7290000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <f aca="false">B24+B30</f>
         <v>10200000</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="B32" s="33" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="B32" s="34" t="n">
         <f aca="false">B29-B31</f>
         <v>0</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="B33" s="33" t="n">
+      <c r="F32" s="20" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B33" s="34" t="n">
         <f aca="false">(B27+B29)/2</f>
         <v>9800000</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="24" t="n">
+      <c r="B34" s="25" t="n">
         <f aca="false">B24-B17</f>
         <v>1982000</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>314</v>
-      </c>
-      <c r="B35" s="33" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="B35" s="34" t="n">
         <f aca="false">(B34+B24)/2</f>
         <v>2446000</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="B36" s="33" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="B36" s="34" t="n">
         <f aca="false">((B27-B34)+B30)/2</f>
         <v>7354000</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
-        <v>316</v>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="C39" s="22" t="s">
+      <c r="B39" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C39" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="23" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B40" s="27" t="n">
+      <c r="B40" s="28" t="n">
         <f aca="false">IF($B$7=0,"",B15/B7)</f>
         <v>0.06</v>
       </c>
-      <c r="C40" s="28" t="n">
+      <c r="C40" s="29" t="n">
         <v>0.075</v>
       </c>
-      <c r="D40" s="20" t="str">
+      <c r="D40" s="21" t="str">
         <f aca="false">IF(B40="","",IF(B40&gt;=C40,"Over normen","Under normen"))</f>
         <v>Under normen</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="27" t="n">
+      <c r="B41" s="28" t="n">
         <f aca="false">IF(B33=0,"",(B16+B13)/B33)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="C41" s="28" t="n">
+      <c r="C41" s="29" t="n">
         <v>0.146</v>
       </c>
-      <c r="D41" s="20" t="str">
+      <c r="D41" s="21" t="str">
         <f aca="false">IF(B41="","",IF(B41&gt;=C41,"Over normen","Under normen"))</f>
         <v>Under normen</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B42" s="27" t="n">
+      <c r="B42" s="28" t="n">
         <f aca="false">IF(B35=0,"",B16/B35)</f>
         <v>0.486508585445626</v>
       </c>
-      <c r="C42" s="28" t="n">
+      <c r="C42" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="D42" s="20" t="str">
+      <c r="D42" s="21" t="str">
         <f aca="false">IF(B42="","",IF(B42&gt;=C42,"Over normen","Under normen"))</f>
         <v>Over normen</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="27" t="n">
+      <c r="B43" s="28" t="n">
         <f aca="false">IF(B26=0,"",B28/B26)</f>
         <v>1.46993318485523</v>
       </c>
-      <c r="C43" s="28" t="n">
+      <c r="C43" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="20" t="str">
+      <c r="D43" s="21" t="str">
         <f aca="false">IF(B43="","",IF(B43&gt;=C43,"Over normen","Under normen"))</f>
         <v>Under normen</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B44" s="27" t="n">
+      <c r="B44" s="28" t="n">
         <f aca="false">IF(B26=0,"",(B28-B21)/B26)</f>
         <v>1.15812917594655</v>
       </c>
-      <c r="C44" s="28" t="n">
+      <c r="C44" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="20" t="str">
+      <c r="D44" s="21" t="str">
         <f aca="false">IF(B44="","",IF(B44&gt;=C44,"Over normen","Under normen"))</f>
         <v>Over normen</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B45" s="27" t="n">
+      <c r="B45" s="28" t="n">
         <f aca="false">IF(B29=0,"",B24/B29)</f>
         <v>0.285294117647059</v>
       </c>
-      <c r="C45" s="28" t="n">
+      <c r="C45" s="29" t="n">
         <v>0.362</v>
       </c>
-      <c r="D45" s="20" t="str">
+      <c r="D45" s="21" t="str">
         <f aca="false">IF(B45="","",IF(B45&gt;=C45,"Over normen","Under normen"))</f>
         <v>Under normen</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="30" t="n">
         <f aca="false">IF(B24=0,"",B30/B24)</f>
         <v>2.50515463917526</v>
       </c>
-      <c r="C46" s="30" t="n">
+      <c r="C46" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="20" t="str">
+      <c r="D46" s="21" t="str">
         <f aca="false">IF(B46="","",IF(B46&lt;=C46,"Innenfor","Over grensen"))</f>
         <v>Innenfor</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="B49" s="26" t="str">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B49" s="27" t="str">
         <f aca="false">IF(B29=0,"Ikke fylt ut ennå",IF(ABS(B32)&lt;1,"OK — de to sidene er like store","AVVIK: differansen står i B32 — du har glemt en post"))</f>
         <v>OK — de to sidene er like store</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="B50" s="26" t="str">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" s="27" t="str">
         <f aca="false">IF(OR(B36=0,B33=0),"Ikke fylt ut ennå",IF((B16+B13)/B33&gt;B13/B36,"OK — den lånte kapitalen tjener mer enn den koster","AVVIK: lånene spiser egenkapitalen"))</f>
         <v>OK — den lånte kapitalen tjener mer enn den koster</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="s">
-        <v>320</v>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4449,329 +4352,329 @@
   <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>326</v>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="D9" s="22" t="s">
+      <c r="B9" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="E9" s="23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <f aca="false">Nøkkeltall!C6</f>
         <v>0.06</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>0.095</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="36" t="n">
         <f aca="false">Nøkkeltall!D6</f>
         <v>0.075</v>
       </c>
-      <c r="E10" s="20" t="str">
+      <c r="E10" s="21" t="str">
         <f aca="false">IF(C10&gt;B10,"B","A")</f>
         <v>B</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <f aca="false">Nøkkeltall!C7</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>0.19</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="36" t="n">
         <f aca="false">Nøkkeltall!D7</f>
         <v>0.146</v>
       </c>
-      <c r="E11" s="20" t="str">
+      <c r="E11" s="21" t="str">
         <f aca="false">IF(C11&gt;B11,"B","A")</f>
         <v>B</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <f aca="false">Nøkkeltall!C8</f>
         <v>0.486508585445626</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="29" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="36" t="n">
         <f aca="false">Nøkkeltall!D8</f>
         <v>0.2</v>
       </c>
-      <c r="E12" s="20" t="str">
+      <c r="E12" s="21" t="str">
         <f aca="false">IF(C12&gt;B12,"B","A")</f>
         <v>B</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <f aca="false">Nøkkeltall!C9</f>
         <v>1.46993318485523</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="29" t="n">
         <v>0.92</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="36" t="n">
         <f aca="false">Nøkkeltall!D9</f>
         <v>2</v>
       </c>
-      <c r="E13" s="20" t="str">
+      <c r="E13" s="21" t="str">
         <f aca="false">IF(C13&gt;B13,"B","A")</f>
         <v>A</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <f aca="false">Nøkkeltall!C10</f>
         <v>1.15812917594655</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="29" t="n">
         <v>0.61</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="36" t="n">
         <f aca="false">Nøkkeltall!D10</f>
         <v>1</v>
       </c>
-      <c r="E14" s="20" t="str">
+      <c r="E14" s="21" t="str">
         <f aca="false">IF(C14&gt;B14,"B","A")</f>
         <v>A</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="32" t="n">
         <f aca="false">Nøkkeltall!C11</f>
         <v>0.285294117647059</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="29" t="n">
         <v>0.12</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="36" t="n">
         <f aca="false">Nøkkeltall!D11</f>
         <v>0.362</v>
       </c>
-      <c r="E15" s="20" t="str">
+      <c r="E15" s="21" t="str">
         <f aca="false">IF(C15&gt;B15,"B","A")</f>
         <v>A</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="33" t="n">
         <f aca="false">Nøkkeltall!C12</f>
         <v>2.50515463917526</v>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">(1-C15)/C15</f>
         <v>7.33333333333333</v>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D16" s="37" t="n">
         <f aca="false">Nøkkeltall!D12</f>
         <v>5</v>
       </c>
-      <c r="E16" s="20" t="str">
+      <c r="E16" s="21" t="str">
         <f aca="false">IF(C16&gt;B16,"B","A")</f>
         <v>B</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="16" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="C20" s="37" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="38" t="n">
         <f aca="false">COUNTIF(E10:E16,"B")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="C21" s="37" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C21" s="38" t="n">
         <f aca="false">C20-IF(E16="B",1,0)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+      <c r="E21" s="20" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="B24" s="26" t="str">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="27" t="str">
         <f aca="false">IF(AND(E10="B",E11="B",E12="B"),"AVVIK: søker B er best på alle tre lønnsomhetstallene. Nettopp derfor er dette en felle — banken hefter for soliditeten, ikke for lønnsomheten","OK — søker B er ikke best på alle lønnsomhetstallene")</f>
         <v>AVVIK: søker B er best på alle tre lønnsomhetstallene. Nettopp derfor er dette en felle — banken hefter for soliditeten, ikke for lønnsomheten</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="B26" s="26" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="27" t="str">
         <f aca="false">IF(C13&gt;=1,"OK — omløpsmidlene dekker den kortsiktige gjelden","AVVIK: likviditetsgrad 1 er under 100 prosent — omløpsmidlene dekker ikke engang gjelden som forfaller i år")</f>
         <v>AVVIK: likviditetsgrad 1 er under 100 prosent — omløpsmidlene dekker ikke engang gjelden som forfaller i år</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="B27" s="26" t="str">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" s="27" t="str">
         <f aca="false">IF(ABS(C16-(1-C15)/C15)&lt;0.001,"OK — de to henger sammen","AVVIK: gjeldsgraden er regnet av noe annet enn egenkapitalandelen")</f>
         <v>OK — de to henger sammen</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
         <v>339</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16" t="s">
-        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4808,778 +4711,778 @@
   <dimension ref="A1:E85"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="54"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>600000</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <f aca="false">Nordlys!B34</f>
         <v>2910000</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <f aca="false">B10-$B$7</f>
         <v>2310000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="B11" s="24" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <f aca="false">Nordlys!B29</f>
         <v>10200000</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <f aca="false">B11-$B$7</f>
         <v>9600000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <f aca="false">Nordlys!B27</f>
         <v>1000000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <f aca="false">B12-$B$7</f>
         <v>400000</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="B13" s="24" t="n">
+      <c r="E12" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <f aca="false">Nordlys!B28</f>
         <v>6600000</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <f aca="false">B13-$B$7</f>
         <v>6000000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="28" t="n">
         <f aca="false">B10/B11</f>
         <v>0.285294117647059</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="28" t="n">
         <f aca="false">C10/C11</f>
         <v>0.240625</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="36" t="n">
         <f aca="false">Nøkkeltall!D11</f>
         <v>0.362</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="E14" s="20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <f aca="false">(B11-B10)/B10</f>
         <v>2.50515463917526</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <f aca="false">(C11-C10)/C10</f>
         <v>3.15584415584416</v>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="37" t="n">
         <f aca="false">Nøkkeltall!D12</f>
         <v>5</v>
       </c>
-      <c r="E15" s="19" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="E15" s="20" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="28" t="n">
         <f aca="false">B13/Nordlys!B40</f>
         <v>1.46993318485523</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">C13/Nordlys!B40</f>
         <v>1.33630289532294</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="36" t="n">
         <f aca="false">Nøkkeltall!D9</f>
         <v>2</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <f aca="false">(B13-Nordlys!B25)/Nordlys!B40</f>
         <v>1.15812917594655</v>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <f aca="false">(C13-Nordlys!B25)/Nordlys!B40</f>
         <v>1.02449888641425</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="36" t="n">
         <f aca="false">Nøkkeltall!D10</f>
         <v>1</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="E17" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="28" t="n">
         <f aca="false">Nordlys!B17/((Nordlys!B47+B10)/2)</f>
         <v>0.486508585445626</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="28" t="n">
         <f aca="false">Nordlys!B17/((Nordlys!B47+C10)/2)</f>
         <v>0.554520037278658</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="36" t="n">
         <f aca="false">Nøkkeltall!D8</f>
         <v>0.2</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="B19" s="32" t="n">
+      <c r="E18" s="20" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="B19" s="33" t="n">
         <f aca="false">$B$7/B12</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="B22" s="26" t="str">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B22" s="27" t="str">
         <f aca="false">IF(C14&lt;B14,"AVVIK: egenkapitalandelen faller og gjeldsgraden stiger. Bedriften blir svakere på alt som betyr noe for banken","OK — utbyttet svekker ikke soliditeten")</f>
         <v>AVVIK: egenkapitalandelen faller og gjeldsgraden stiger. Bedriften blir svakere på alt som betyr noe for banken</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="B24" s="26" t="str">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B24" s="27" t="str">
         <f aca="false">IF(C18&gt;B18,"AVVIK: egenkapitalrentabiliteten STIGER av utbyttet, samtidig som alt annet blir svakere. Et høyt tall kan være et faresignal","OK — egenkapitalrentabiliteten stiger ikke")</f>
         <v>AVVIK: egenkapitalrentabiliteten STIGER av utbyttet, samtidig som alt annet blir svakere. Et høyt tall kan være et faresignal</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="B26" s="26" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="27" t="str">
         <f aca="false">IF(C12&gt;=0,"OK — bankinnskuddet dekker utbyttet, men se hva som blir igjen til lønn og merverdiavgift","AVVIK: bankinnskuddet dekker ikke utbyttet — pengene må hentes fra kassekreditten")</f>
         <v>OK — bankinnskuddet dekker utbyttet, men se hva som blir igjen til lønn og merverdiavgift</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="B32" s="24" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="B32" s="25" t="n">
         <f aca="false">Nordlys!B51</f>
         <v>7354000</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="B33" s="24" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="B33" s="25" t="n">
         <f aca="false">Nordlys!B16</f>
         <v>210000</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="B34" s="31" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B34" s="32" t="n">
         <f aca="false">B33/B32</f>
         <v>0.0285558879521349</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="B35" s="28" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="B35" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="E35" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="B36" s="25" t="n">
+      <c r="E35" s="20" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="B36" s="26" t="n">
         <f aca="false">B32*B35</f>
         <v>441240</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="B37" s="25" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B37" s="26" t="n">
         <f aca="false">Nordlys!B14+Nordlys!B15-B36</f>
         <v>958760</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="27" t="n">
+      <c r="B38" s="28" t="n">
         <f aca="false">(B37+B36)/Nordlys!B49</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="E38" s="19" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
+      <c r="E38" s="20" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="B39" s="27" t="n">
+      <c r="B39" s="28" t="n">
         <f aca="false">B37/Nordlys!B50</f>
         <v>0.391970564186427</v>
       </c>
-      <c r="E39" s="19" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="B40" s="32" t="n">
+      <c r="E39" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="B40" s="33" t="n">
         <f aca="false">(B38-B35)*100</f>
         <v>8.28571428571429</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="B41" s="27" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B41" s="28" t="n">
         <f aca="false">(Nordlys!B14+Nordlys!B15)/B32</f>
         <v>0.190372586347566</v>
       </c>
-      <c r="E41" s="19" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
+      <c r="E41" s="20" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="B44" s="26" t="str">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="B44" s="27" t="str">
         <f aca="false">IF(B38&gt;B35,"OK — den lånte kapitalen tjener fortsatt mer enn den koster","AVVIK: lånerenta har passert totalkapitalrentabiliteten. Nå spiser gjelden egenkapitalen i stedet for å løfte den")</f>
         <v>OK — den lånte kapitalen tjener fortsatt mer enn den koster</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="B45" s="26" t="str">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B45" s="27" t="str">
         <f aca="false">IF(ABS(B38-Nøkkeltall!C7)&lt;0.0001,"OK — totalkapitalrentabiliteten er den samme uansett hva renta er. Det er nettopp derfor rentene legges tilbake i telleren","AVVIK: sjekk formlene — TKR skal ikke endre seg av renta alene")</f>
         <v>OK — totalkapitalrentabiliteten er den samme uansett hva renta er. Det er nettopp derfor rentene legges tilbake i telleren</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="s">
-        <v>389</v>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22"/>
-      <c r="B51" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>392</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19" t="s">
-        <v>394</v>
-      </c>
-      <c r="B52" s="24" t="n">
+      <c r="A51" s="23"/>
+      <c r="B51" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="B52" s="25" t="n">
         <f aca="false">Nordlys!$B$5</f>
         <v>22400000</v>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="25" t="n">
         <f aca="false">Nordlys!$B$5</f>
         <v>22400000</v>
       </c>
-      <c r="E52" s="19" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="s">
+      <c r="E52" s="20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B53" s="28" t="n">
+      <c r="B53" s="29" t="n">
         <v>0.088</v>
       </c>
-      <c r="C53" s="28" t="n">
+      <c r="C53" s="29" t="n">
         <v>0.042</v>
       </c>
-      <c r="D53" s="35" t="n">
+      <c r="D53" s="36" t="n">
         <f aca="false">Nøkkeltall!D6</f>
         <v>0.075</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="28" t="n">
+      <c r="B54" s="29" t="n">
         <v>0.175</v>
       </c>
-      <c r="C54" s="28" t="n">
+      <c r="C54" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="D54" s="35" t="n">
+      <c r="D54" s="36" t="n">
         <f aca="false">Nøkkeltall!D7</f>
         <v>0.146</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B55" s="28" t="n">
+      <c r="B55" s="29" t="n">
         <v>0.62</v>
       </c>
-      <c r="C55" s="28" t="n">
+      <c r="C55" s="29" t="n">
         <v>0.125</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B56" s="28" t="n">
+      <c r="B56" s="29" t="n">
         <v>1.18</v>
       </c>
-      <c r="C56" s="28" t="n">
+      <c r="C56" s="29" t="n">
         <v>2.1</v>
       </c>
-      <c r="D56" s="35" t="n">
+      <c r="D56" s="36" t="n">
         <f aca="false">Nøkkeltall!D9</f>
         <v>2</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="19" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B57" s="28" t="n">
+      <c r="B57" s="29" t="n">
         <v>0.78</v>
       </c>
-      <c r="C57" s="28" t="n">
+      <c r="C57" s="29" t="n">
         <v>1.55</v>
       </c>
-      <c r="D57" s="35" t="n">
+      <c r="D57" s="36" t="n">
         <f aca="false">Nøkkeltall!D10</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B58" s="28" t="n">
+      <c r="B58" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="C58" s="28" t="n">
+      <c r="C58" s="29" t="n">
         <v>0.52</v>
       </c>
-      <c r="D58" s="35" t="n">
+      <c r="D58" s="36" t="n">
         <f aca="false">Nøkkeltall!D11</f>
         <v>0.362</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="B59" s="32" t="n">
+      <c r="B59" s="33" t="n">
         <f aca="false">(1-B58)/B58</f>
         <v>4.55555555555556</v>
       </c>
-      <c r="C59" s="32" t="n">
+      <c r="C59" s="33" t="n">
         <f aca="false">(1-C58)/C58</f>
         <v>0.923076923076923</v>
       </c>
-      <c r="D59" s="36" t="n">
+      <c r="D59" s="37" t="n">
         <f aca="false">Nøkkeltall!D12</f>
         <v>5</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="B60" s="23" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B60" s="24" t="n">
         <v>6000000</v>
       </c>
-      <c r="C60" s="23" t="n">
+      <c r="C60" s="24" t="n">
         <v>9500000</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="17" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="18" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="B63" s="25" t="n">
+      <c r="B63" s="26" t="n">
         <f aca="false">B52*B53</f>
         <v>1971200</v>
       </c>
-      <c r="C63" s="25" t="n">
+      <c r="C63" s="26" t="n">
         <f aca="false">C52*C53</f>
         <v>940800</v>
       </c>
-      <c r="E63" s="19" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="B64" s="24" t="n">
+      <c r="E63" s="20" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="B64" s="25" t="n">
         <f aca="false">B63/B54</f>
         <v>11264000</v>
       </c>
-      <c r="C64" s="24" t="n">
+      <c r="C64" s="25" t="n">
         <f aca="false">C63/C54</f>
         <v>11760000</v>
       </c>
-      <c r="E64" s="19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="B65" s="25" t="n">
+      <c r="E64" s="20" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="B65" s="26" t="n">
         <f aca="false">B64*B58</f>
         <v>2027520</v>
       </c>
-      <c r="C65" s="25" t="n">
+      <c r="C65" s="26" t="n">
         <f aca="false">C64*C58</f>
         <v>6115200</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="B66" s="25" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="B66" s="26" t="n">
         <f aca="false">B64-B65</f>
         <v>9236480</v>
       </c>
-      <c r="C66" s="25" t="n">
+      <c r="C66" s="26" t="n">
         <f aca="false">C64-C65</f>
         <v>5644800</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="B67" s="24" t="n">
+      <c r="B67" s="25" t="n">
         <f aca="false">B55*B65</f>
         <v>1257062.4</v>
       </c>
-      <c r="C67" s="24" t="n">
+      <c r="C67" s="25" t="n">
         <f aca="false">C55*C65</f>
         <v>764400</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="B68" s="24" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="B68" s="25" t="n">
         <f aca="false">B63-B67</f>
         <v>714137.6</v>
       </c>
-      <c r="C68" s="24" t="n">
+      <c r="C68" s="25" t="n">
         <f aca="false">C63-C67</f>
         <v>176400</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="B69" s="31" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="B69" s="32" t="n">
         <f aca="false">B68/B66</f>
         <v>0.0773170731707317</v>
       </c>
-      <c r="C69" s="31" t="n">
+      <c r="C69" s="32" t="n">
         <f aca="false">C68/C66</f>
         <v>0.03125</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="19" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="32" t="n">
+      <c r="B70" s="33" t="n">
         <f aca="false">(B54-B69)*100</f>
         <v>9.76829268292683</v>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C70" s="33" t="n">
         <f aca="false">(C54-C69)*100</f>
         <v>4.875</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="B73" s="32" t="n">
+      <c r="E70" s="20" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="B73" s="33" t="n">
         <f aca="false">B60/B65</f>
         <v>2.9592803030303</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C73" s="33" t="n">
         <f aca="false">C60/C65</f>
         <v>1.55350601779173</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="B74" s="27" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="B74" s="28" t="n">
         <f aca="false">B67/B60</f>
         <v>0.2095104</v>
       </c>
-      <c r="C74" s="27" t="n">
+      <c r="C74" s="28" t="n">
         <f aca="false">C67/C60</f>
         <v>0.0804631578947369</v>
       </c>
-      <c r="E74" s="19" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="B75" s="25" t="n">
+      <c r="E74" s="20" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="B75" s="26" t="n">
         <f aca="false">B60+B66</f>
         <v>15236480</v>
       </c>
-      <c r="C75" s="25" t="n">
+      <c r="C75" s="26" t="n">
         <f aca="false">C60+C66</f>
         <v>15144800</v>
       </c>
-      <c r="E75" s="19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="B76" s="33" t="n">
+      <c r="E75" s="20" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="B76" s="34" t="n">
         <f aca="false">ABS(B75-C75)</f>
         <v>91680</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="B77" s="31" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="B77" s="32" t="n">
         <f aca="false">B76/B75</f>
         <v>0.00601713781660856</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="17" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="B80" s="26" t="str">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="B80" s="27" t="str">
         <f aca="false">IF(B77&lt;0.05,"AVVIK: de to bedriftene koster praktisk talt det samme når gjelden regnes med. Prisantydningene alene sier deg altså ingenting","OK — de to koster ulikt også når gjelden regnes med")</f>
         <v>AVVIK: de to bedriftene koster praktisk talt det samme når gjelden regnes med. Prisantydningene alene sier deg altså ingenting</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="B82" s="26" t="str">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="17" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B82" s="27" t="str">
         <f aca="false">IF(AND(B68&gt;0,C68&gt;0),"OK — regnestykket henger sammen for begge bedriftene","AVVIK: negative rentekostnader betyr at egenkapitalrentabiliteten er satt for høyt i forhold til driftsmarginen")</f>
         <v>OK — regnestykket henger sammen for begge bedriftene</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="B83" s="26" t="str">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="B83" s="27" t="str">
         <f aca="false">IF(AND(B54&gt;B69,C54&gt;C69),"OK — begge tjener mer på kapitalen enn den koster","AVVIK: minst én av bedriftene taper på gjelden sin")</f>
         <v>OK — begge tjener mer på kapitalen enn den koster</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="s">
-        <v>418</v>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="17" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok04/OK04_Regnskapsanalyse_Regneark_Nokkeltall.xlsx
+++ b/pensum/ok04/OK04_Regnskapsanalyse_Regneark_Nokkeltall.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="410">
-  <si>
-    <t xml:space="preserve">Hvorfor får eierne 48,7 prosent? Den enkle versjonen</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="409">
+  <si>
+    <t xml:space="preserve">Hvorfor får eierne 47,9 prosent? Den enkle versjonen</t>
   </si>
   <si>
     <t xml:space="preserve">Fyll inn de fire gule cellene. Svaret står i den grønne. Alt annet regner seg selv. Vil du gå dypere, ligger alle sju nøkkeltallene i arkene bak.</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">Det som ikke er eiernes, er lånt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lånerente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rentene delt på gjelden. Det lånet koster.</t>
+    <t xml:space="preserve">Gjennomsnittlig gjeldsrente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rentene delt på all gjeld, også den rentefrie. Banken tar 7,5 % på lånene.</t>
   </si>
   <si>
     <t xml:space="preserve">EGENKAPITALRENTABILITET</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Hva eierne får igjen på sine egne penger.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hele kapitalen minus lånerenta, i prosentpoeng</t>
+    <t xml:space="preserve">Hele kapitalen minus gjeldsrenta, i prosentpoeng</t>
   </si>
   <si>
     <t xml:space="preserve">Så mye mer tjener de lånte pengene enn de koster. Blir tallet negativt, spises egenkapitalen.</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Enkelt</t>
   </si>
   <si>
-    <t xml:space="preserve">Start her. Fire gule celler, ett svar. Hvorfor eierne får 48,7 prosent når hele kapitalen tjener 14,3.</t>
+    <t xml:space="preserve">Start her. Fire gule celler, ett svar. Hvorfor eierne får 47,9 prosent når hele kapitalen tjener 14,3.</t>
   </si>
   <si>
     <t xml:space="preserve">Fra kapittel 3</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">2 · Balanse pr. 31.12.2026 — eiendeler</t>
   </si>
   <si>
-    <t xml:space="preserve">Maskiner og verktøy</t>
+    <t xml:space="preserve">Verktøy og måleinstrumenter</t>
   </si>
   <si>
     <t xml:space="preserve">Biler</t>
@@ -623,13 +623,10 @@
     <t xml:space="preserve">2 · Sammenhengen som er kapitlets poeng</t>
   </si>
   <si>
-    <t xml:space="preserve">Gjennomsnittlig lånerente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rentekostnader delt på gjennomsnittlig gjeld.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin: TKR minus lånerente, i prosentpoeng</t>
+    <t xml:space="preserve">Rentekostnader delt på gjennomsnittlig gjeld, også den rentefrie. Banken tar 7,5 % på lån og kassekreditt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin: TKR minus gjeldsrente, i prosentpoeng</t>
   </si>
   <si>
     <t xml:space="preserve">Så mye kan lønnsomheten falle før gjelden begynner å spise egenkapitalen.</t>
@@ -761,7 +758,7 @@
     <t xml:space="preserve">For lavt. Skattekostnaden sier lite om hvor godt bedriften drives.</t>
   </si>
   <si>
-    <t xml:space="preserve">Er totalkapitalrentabiliteten høyere enn lånerenta?</t>
+    <t xml:space="preserve">Er totalkapitalrentabiliteten høyere enn gjeldsrenta?</t>
   </si>
   <si>
     <t xml:space="preserve">Er likviditetsgrad 2 lavere enn grad 1?</t>
@@ -1130,10 +1127,10 @@
     <t xml:space="preserve">Rentekostnader i dag</t>
   </si>
   <si>
-    <t xml:space="preserve">Gjennomsnittlig lånerente i dag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ny lånerente</t>
+    <t xml:space="preserve">Gjennomsnittlig gjeldsrente i dag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ny gjeldsrente, snitt av all gjeld (15 % på lånene, det dobbelte av i dag)</t>
   </si>
   <si>
     <t xml:space="preserve">Endre denne. Hvor høyt må den før eierne taper på gjelden?</t>
@@ -1151,7 +1148,7 @@
     <t xml:space="preserve">Faller når renta stiger. Her ligger hele risikoen ved gjeldsgraden.</t>
   </si>
   <si>
-    <t xml:space="preserve">Margin: TKR minus ny lånerente, i prosentpoeng</t>
+    <t xml:space="preserve">Margin: TKR minus ny gjeldsrente, i prosentpoeng</t>
   </si>
   <si>
     <t xml:space="preserve">Renta som gir null igjen til eierne</t>
@@ -1160,7 +1157,7 @@
     <t xml:space="preserve">Ved denne renta spiser rentekostnadene hele driftsresultatet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Er totalkapitalrentabiliteten fortsatt høyere enn lånerenta?</t>
+    <t xml:space="preserve">Er totalkapitalrentabiliteten fortsatt høyere enn gjeldsrenta?</t>
   </si>
   <si>
     <t xml:space="preserve">Er totalkapitalrentabiliteten uavhengig av renta?</t>
@@ -1214,7 +1211,7 @@
     <t xml:space="preserve">= Rentekostnader</t>
   </si>
   <si>
-    <t xml:space="preserve">= Gjennomsnittlig lånerente</t>
+    <t xml:space="preserve">= Gjennomsnittlig gjeldsrente</t>
   </si>
   <si>
     <t xml:space="preserve">Så mye kan lønnsomheten falle før eierne begynner å tape på gjelden.</t>
@@ -1253,7 +1250,7 @@
     <t xml:space="preserve">Er rentekostnadene positive for begge?</t>
   </si>
   <si>
-    <t xml:space="preserve">Ligger begge over sin egen lånerente?</t>
+    <t xml:space="preserve">Ligger begge over sin egen gjeldsrente?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet, kap. 4.2.1 til 4.2.4. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent. De to bedriftene i scenario C er konstruert for øvingen, men utledet: hver av dem er gitt fire nøkkeltall og den samme omsetningen som Nordlys, og alt annet regnes av dem.</t>
@@ -1916,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1190000</v>
+        <v>1167500</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>4</v>
@@ -1927,7 +1924,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>210000</v>
+        <v>232500</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>6</v>
@@ -1938,7 +1935,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>9800000</v>
+        <v>9791325</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>8</v>
@@ -1949,7 +1946,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>2446000</v>
+        <v>2437325</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>10</v>
@@ -1981,7 +1978,7 @@
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">B11/B7</f>
-        <v>0.142857142857143</v>
+        <v>0.142983712623164</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>15</v>
@@ -2005,7 +2002,7 @@
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">B6/B13</f>
-        <v>0.0285558879521349</v>
+        <v>0.0316154473755779</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>19</v>
@@ -2018,7 +2015,7 @@
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">B5/B8</f>
-        <v>0.486508585445626</v>
+        <v>0.479008749346107</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>21</v>
@@ -2030,7 +2027,7 @@
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">(B12-B14)*100</f>
-        <v>11.4301254905008</v>
+        <v>11.1368265247586</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>23</v>
@@ -2047,7 +2044,7 @@
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="str">
         <f aca="false">"Eierne får "&amp;TEXT(B16,"0.0 %")&amp;" på pengene sine, mens hele kapitalen tjener "&amp;TEXT(B12,"0.0 %")&amp;". Forskjellen kommer av at lånet koster "&amp;TEXT(B14,"0.0 %")&amp;" og egenkapitalen er liten."</f>
-        <v>Eierne får 48.7 % på pengene sine, mens hele kapitalen tjener 14.3 %. Forskjellen kommer av at lånet koster 2.9 % og egenkapitalen er liten.</v>
+        <v>Eierne får 47.9 % på pengene sine, mens hele kapitalen tjener 14.3 %. Forskjellen kommer av at lånet koster 3.2 % og egenkapitalen er liten.</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -2606,7 +2603,7 @@
         <v>122</v>
       </c>
       <c r="B16" s="24" t="n">
-        <v>210000</v>
+        <v>232500</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>123</v>
@@ -2618,7 +2615,7 @@
       </c>
       <c r="B17" s="26" t="n">
         <f aca="false">B14+B15-B16</f>
-        <v>1190000</v>
+        <v>1167500</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>125</v>
@@ -2629,7 +2626,7 @@
         <v>126</v>
       </c>
       <c r="B18" s="24" t="n">
-        <v>262000</v>
+        <v>256850</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2638,7 +2635,7 @@
       </c>
       <c r="B19" s="26" t="n">
         <f aca="false">B17-B18</f>
-        <v>928000</v>
+        <v>910650</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>128</v>
@@ -2701,7 +2698,7 @@
         <v>137</v>
       </c>
       <c r="B27" s="24" t="n">
-        <v>1000000</v>
+        <v>982650</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2710,7 +2707,7 @@
       </c>
       <c r="B28" s="26" t="n">
         <f aca="false">B25+B26+B27</f>
-        <v>6600000</v>
+        <v>6582650</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2719,7 +2716,7 @@
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B24+B28</f>
-        <v>10200000</v>
+        <v>10182650</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2740,7 +2737,7 @@
         <v>142</v>
       </c>
       <c r="B33" s="24" t="n">
-        <v>2610000</v>
+        <v>2592650</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2749,7 +2746,7 @@
       </c>
       <c r="B34" s="26" t="n">
         <f aca="false">B32+B33</f>
-        <v>2910000</v>
+        <v>2892650</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2819,7 +2816,7 @@
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">B34+B41</f>
-        <v>10200000</v>
+        <v>10182650</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2874,7 +2871,7 @@
       </c>
       <c r="B49" s="26" t="n">
         <f aca="false">(B46+B29)/2</f>
-        <v>9800000</v>
+        <v>9791325</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>161</v>
@@ -2886,7 +2883,7 @@
       </c>
       <c r="B50" s="26" t="n">
         <f aca="false">(B47+B34)/2</f>
-        <v>2446000</v>
+        <v>2437325</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>163</v>
@@ -3037,7 +3034,7 @@
       </c>
       <c r="C7" s="28" t="n">
         <f aca="false">(Nordlys!B17+Nordlys!B16)/Nordlys!B49</f>
-        <v>0.142857142857143</v>
+        <v>0.142983712623164</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>0.146</v>
@@ -3059,7 +3056,7 @@
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">Nordlys!B17/Nordlys!B50</f>
-        <v>0.486508585445626</v>
+        <v>0.479008749346107</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>0.2</v>
@@ -3081,7 +3078,7 @@
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">Nordlys!B28/Nordlys!B40</f>
-        <v>1.46993318485523</v>
+        <v>1.46606904231626</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>2</v>
@@ -3103,7 +3100,7 @@
       </c>
       <c r="C10" s="28" t="n">
         <f aca="false">(Nordlys!B28-Nordlys!B25)/Nordlys!B40</f>
-        <v>1.15812917594655</v>
+        <v>1.15426503340757</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>1</v>
@@ -3125,7 +3122,7 @@
       </c>
       <c r="C11" s="28" t="n">
         <f aca="false">Nordlys!B34/Nordlys!B29</f>
-        <v>0.285294117647059</v>
+        <v>0.284076345548556</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>0.362</v>
@@ -3147,7 +3144,7 @@
       </c>
       <c r="C12" s="30" t="n">
         <f aca="false">Nordlys!B41/Nordlys!B34</f>
-        <v>2.50515463917526</v>
+        <v>2.52018045736608</v>
       </c>
       <c r="D12" s="31" t="n">
         <v>5</v>
@@ -3167,83 +3164,83 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">Nordlys!B16/Nordlys!B51</f>
-        <v>0.0285558879521349</v>
+        <v>0.0316154473755779</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C16" s="33" t="n">
         <f aca="false">(C7-C15)*100</f>
-        <v>11.4301254905008</v>
+        <v>11.1368265247586</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" s="33" t="n">
         <f aca="false">C8/C7</f>
-        <v>3.40556009811938</v>
+        <v>3.35009310192234</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C18" s="34" t="n">
         <f aca="false">Nordlys!B28-Nordlys!B40</f>
-        <v>2110000</v>
+        <v>2092650</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C19" s="32" t="n">
         <f aca="false">Nordlys!B9/Nordlys!B8</f>
         <v>1.66984505363528</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B22" s="29" t="n">
         <v>0.25</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C23" s="34" t="n">
         <f aca="false">Nordlys!B5*(1+B22)</f>
@@ -3252,14 +3249,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C24" s="34" t="n">
         <f aca="false">Nordlys!B8*(1+B22)</f>
         <v>10487500</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3280,161 +3277,161 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>214</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>215</v>
       </c>
       <c r="C27" s="30" t="n">
         <f aca="false">Nordlys!B26*360/C23</f>
         <v>54</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>217</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>218</v>
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">Nordlys!B36*360/C24</f>
         <v>72.0858164481526</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>220</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>221</v>
       </c>
       <c r="C29" s="30" t="n">
         <f aca="false">Nordlys!B8/Nordlys!B25</f>
         <v>5.99285714285714</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B30" s="20" t="s">
         <v>223</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>224</v>
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">360/C29</f>
         <v>60.0715137067938</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>226</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>227</v>
       </c>
       <c r="C31" s="30" t="n">
         <f aca="false">Nordlys!B5/Nordlys!B49</f>
-        <v>2.28571428571429</v>
+        <v>2.28773940197062</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B33" s="35" t="n">
         <v>20</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C34" s="33" t="n">
         <f aca="false">C27-B33</f>
         <v>34</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C35" s="34" t="n">
         <f aca="false">C23*10/360</f>
         <v>777777.777777778</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>236</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>237</v>
       </c>
       <c r="C38" s="32" t="n">
         <f aca="false">(Nordlys!B17+Nordlys!B16)/Nordlys!B5</f>
         <v>0.0625</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C41" s="32" t="n">
         <f aca="false">Nordlys!B17/Nordlys!B49</f>
-        <v>0.121428571428571</v>
+        <v>0.119238203205388</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C42" s="32" t="n">
         <f aca="false">Nordlys!B19/Nordlys!B50</f>
-        <v>0.379394930498774</v>
+        <v>0.373626824489963</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3444,7 +3441,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B45" s="27" t="str">
         <f aca="false">IF(C7&gt;C15,"OK — den lånte kapitalen tjener mer enn den koster, og differansen tilfaller eierne","AVVIK: lånene spiser egenkapitalen — da virker gjeldsgraden mot eierne i stedet for for dem")</f>
@@ -3453,7 +3450,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B46" s="27" t="str">
         <f aca="false">IF(C10&lt;=C9,"OK — grad 2 er alltid lavest, fordi varelageret er trukket ut","AVVIK: varelageret kan ikke være negativt")</f>
@@ -3462,7 +3459,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B47" s="27" t="str">
         <f aca="false">IF(ABS(C12-(1-C11)/C11)&lt;0.001,"OK — gjeldsgraden og egenkapitalandelen sier det samme to ganger. Den ene er den andre snudd på hodet","AVVIK: de to henger ikke sammen")</f>
@@ -3471,7 +3468,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B48" s="27" t="str">
         <f aca="false">IF(C11&gt;=D11,"OK — egenkapitalandelen er på eller over bransjens nivå","AVVIK: egenkapitalandelen ligger under bransjen. Det er det første banken ser")</f>
@@ -3480,12 +3477,12 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B50" s="27" t="str">
         <f aca="false">IF(C30+C27-C28&gt;0,"OK — og det er nettopp derfor kassekreditten brukes: fra kabelen kjøpes til kunden betaler går det "&amp;TEXT(C30+C27,"0")&amp;" dager, grossisten finansierer "&amp;TEXT(C28,"0")&amp;" av dem, og de siste "&amp;TEXT(C30+C27-C28,"0")&amp;" må Nordlys finansiere selv","AVVIK: da finansierer leverandørene hele driften, og kassekreditten skulle vært unødvendig")</f>
@@ -3494,22 +3491,22 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3567,45 +3564,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="23" t="s">
         <v>258</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B6" s="26" t="n">
         <f aca="false">Nordlys!B5</f>
         <v>22400000</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">Nordlys!B14</f>
@@ -3617,14 +3614,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B8" s="26" t="n">
         <f aca="false">Nordlys!B17</f>
-        <v>1190000</v>
+        <v>1167500</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3633,46 +3630,46 @@
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">Nordlys!B16</f>
-        <v>210000</v>
+        <v>232500</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">Nordlys!B29</f>
-        <v>10200000</v>
+        <v>10182650</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">Nordlys!B34</f>
-        <v>2910000</v>
+        <v>2892650</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">Nordlys!B28</f>
-        <v>6600000</v>
+        <v>6582650</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3684,57 +3681,57 @@
         <v>1400000</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">Nordlys!B40</f>
         <v>4490000</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B17" s="34" t="n">
         <f aca="false">Nordlys!B46</f>
         <v>9400000</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>278</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>280</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3743,10 +3740,10 @@
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">Nøkkeltall!C11</f>
-        <v>0.285294117647059</v>
+        <v>0.284076345548556</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3755,7 +3752,7 @@
       </c>
       <c r="B23" s="33" t="n">
         <f aca="false">Nøkkeltall!C12</f>
-        <v>2.50515463917526</v>
+        <v>2.52018045736608</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3764,7 +3761,7 @@
       </c>
       <c r="B24" s="32" t="n">
         <f aca="false">Nøkkeltall!C9</f>
-        <v>1.46993318485523</v>
+        <v>1.46606904231626</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3773,12 +3770,12 @@
       </c>
       <c r="B25" s="32" t="n">
         <f aca="false">Nøkkeltall!C10</f>
-        <v>1.15812917594655</v>
+        <v>1.15426503340757</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3790,7 +3787,7 @@
         <v>0.06</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3799,10 +3796,10 @@
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">Nøkkeltall!C7</f>
-        <v>0.142857142857143</v>
+        <v>0.142983712623164</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3811,10 +3808,10 @@
       </c>
       <c r="B30" s="32" t="n">
         <f aca="false">Nøkkeltall!C8</f>
-        <v>0.486508585445626</v>
+        <v>0.479008749346107</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3824,7 +3821,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B33" s="27" t="str">
         <f aca="false">IF(AND(B6=Nordlys!B5,B10=Nordlys!B29,B11=Nordlys!B34,B14=Nordlys!B40),"OK — alle er formler. Endrer du en post i arket Nordlys, endrer nøkkeltallet seg overalt","AVVIK: en av koblingene er brutt")</f>
@@ -3833,7 +3830,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B34" s="27" t="str">
         <f aca="false">IF(ABS(B10-Nordlys!B24-B12)&lt;1,"OK — sum eiendeler er anleggsmidler pluss omløpsmidler","AVVIK: balansetallene henger ikke sammen")</f>
@@ -3842,12 +3839,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -3888,23 +3885,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>295</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>296</v>
       </c>
       <c r="E4" s="35" t="n">
         <v>2026</v>
@@ -3912,12 +3909,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>22400000</v>
@@ -3968,7 +3965,7 @@
         <v>122</v>
       </c>
       <c r="B13" s="24" t="n">
-        <v>210000</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3976,7 +3973,7 @@
         <v>126</v>
       </c>
       <c r="B14" s="24" t="n">
-        <v>262000</v>
+        <v>256850</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3994,7 +3991,7 @@
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">B15+B12-B13</f>
-        <v>1190000</v>
+        <v>1167500</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4003,12 +4000,12 @@
       </c>
       <c r="B17" s="26" t="n">
         <f aca="false">B16-B14</f>
-        <v>928000</v>
+        <v>910650</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4037,23 +4034,23 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B23" s="24" t="n">
-        <v>1000000</v>
+        <v>982650</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B24" s="24" t="n">
-        <v>2910000</v>
+        <v>2892650</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B25" s="24" t="n">
         <v>2800000</v>
@@ -4061,7 +4058,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B26" s="24" t="n">
         <v>4490000</v>
@@ -4081,7 +4078,7 @@
       </c>
       <c r="B28" s="26" t="n">
         <f aca="false">B21+B22+B23</f>
-        <v>6600000</v>
+        <v>6582650</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4090,12 +4087,12 @@
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B20+B28</f>
-        <v>10200000</v>
+        <v>10182650</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B30" s="26" t="n">
         <f aca="false">B25+B26</f>
@@ -4108,28 +4105,28 @@
       </c>
       <c r="B31" s="26" t="n">
         <f aca="false">B24+B30</f>
-        <v>10200000</v>
+        <v>10182650</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B32" s="34" t="n">
         <f aca="false">B29-B31</f>
         <v>0</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" s="34" t="n">
         <f aca="false">(B27+B29)/2</f>
-        <v>9800000</v>
+        <v>9791325</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4143,16 +4140,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B35" s="34" t="n">
         <f aca="false">(B34+B24)/2</f>
-        <v>2446000</v>
+        <v>2437325</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B36" s="34" t="n">
         <f aca="false">((B27-B34)+B30)/2</f>
@@ -4161,7 +4158,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4169,7 +4166,7 @@
         <v>47</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C39" s="23" t="s">
         <v>174</v>
@@ -4200,7 +4197,7 @@
       </c>
       <c r="B41" s="28" t="n">
         <f aca="false">IF(B33=0,"",(B16+B13)/B33)</f>
-        <v>0.142857142857143</v>
+        <v>0.142983712623164</v>
       </c>
       <c r="C41" s="29" t="n">
         <v>0.146</v>
@@ -4216,7 +4213,7 @@
       </c>
       <c r="B42" s="28" t="n">
         <f aca="false">IF(B35=0,"",B16/B35)</f>
-        <v>0.486508585445626</v>
+        <v>0.479008749346107</v>
       </c>
       <c r="C42" s="29" t="n">
         <v>0.2</v>
@@ -4232,7 +4229,7 @@
       </c>
       <c r="B43" s="28" t="n">
         <f aca="false">IF(B26=0,"",B28/B26)</f>
-        <v>1.46993318485523</v>
+        <v>1.46606904231626</v>
       </c>
       <c r="C43" s="29" t="n">
         <v>2</v>
@@ -4248,7 +4245,7 @@
       </c>
       <c r="B44" s="28" t="n">
         <f aca="false">IF(B26=0,"",(B28-B21)/B26)</f>
-        <v>1.15812917594655</v>
+        <v>1.15426503340757</v>
       </c>
       <c r="C44" s="29" t="n">
         <v>1</v>
@@ -4264,7 +4261,7 @@
       </c>
       <c r="B45" s="28" t="n">
         <f aca="false">IF(B29=0,"",B24/B29)</f>
-        <v>0.285294117647059</v>
+        <v>0.284076345548556</v>
       </c>
       <c r="C45" s="29" t="n">
         <v>0.362</v>
@@ -4280,7 +4277,7 @@
       </c>
       <c r="B46" s="30" t="n">
         <f aca="false">IF(B24=0,"",B30/B24)</f>
-        <v>2.50515463917526</v>
+        <v>2.52018045736608</v>
       </c>
       <c r="C46" s="31" t="n">
         <v>5</v>
@@ -4297,7 +4294,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B49" s="27" t="str">
         <f aca="false">IF(B29=0,"Ikke fylt ut ennå",IF(ABS(B32)&lt;1,"OK — de to sidene er like store","AVVIK: differansen står i B32 — du har glemt en post"))</f>
@@ -4306,7 +4303,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B50" s="27" t="str">
         <f aca="false">IF(OR(B36=0,B33=0),"Ikke fylt ut ennå",IF((B16+B13)/B33&gt;B13/B36,"OK — den lånte kapitalen tjener mer enn den koster","AVVIK: lånene spiser egenkapitalen"))</f>
@@ -4315,12 +4312,12 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4361,32 +4358,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4394,16 +4391,16 @@
         <v>47</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>318</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>319</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>174</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4432,7 +4429,7 @@
       </c>
       <c r="B11" s="32" t="n">
         <f aca="false">Nøkkeltall!C7</f>
-        <v>0.142857142857143</v>
+        <v>0.142983712623164</v>
       </c>
       <c r="C11" s="29" t="n">
         <v>0.19</v>
@@ -4452,7 +4449,7 @@
       </c>
       <c r="B12" s="32" t="n">
         <f aca="false">Nøkkeltall!C8</f>
-        <v>0.486508585445626</v>
+        <v>0.479008749346107</v>
       </c>
       <c r="C12" s="29" t="n">
         <v>0.95</v>
@@ -4472,7 +4469,7 @@
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">Nøkkeltall!C9</f>
-        <v>1.46993318485523</v>
+        <v>1.46606904231626</v>
       </c>
       <c r="C13" s="29" t="n">
         <v>0.92</v>
@@ -4492,7 +4489,7 @@
       </c>
       <c r="B14" s="32" t="n">
         <f aca="false">Nøkkeltall!C10</f>
-        <v>1.15812917594655</v>
+        <v>1.15426503340757</v>
       </c>
       <c r="C14" s="29" t="n">
         <v>0.61</v>
@@ -4512,7 +4509,7 @@
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">Nøkkeltall!C11</f>
-        <v>0.285294117647059</v>
+        <v>0.284076345548556</v>
       </c>
       <c r="C15" s="29" t="n">
         <v>0.12</v>
@@ -4532,7 +4529,7 @@
       </c>
       <c r="B16" s="33" t="n">
         <f aca="false">Nøkkeltall!C12</f>
-        <v>2.50515463917526</v>
+        <v>2.52018045736608</v>
       </c>
       <c r="C16" s="33" t="n">
         <f aca="false">(1-C15)/C15</f>
@@ -4549,17 +4546,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E17" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C20" s="38" t="n">
         <f aca="false">COUNTIF(E10:E16,"B")</f>
@@ -4568,14 +4565,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C21" s="38" t="n">
         <f aca="false">C20-IF(E16="B",1,0)</f>
         <v>3</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4585,7 +4582,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B24" s="27" t="str">
         <f aca="false">IF(AND(E10="B",E11="B",E12="B"),"AVVIK: søker B er best på alle tre lønnsomhetstallene. Nettopp derfor er dette en felle — banken hefter for soliditeten, ikke for lønnsomheten","OK — søker B er ikke best på alle lønnsomhetstallene")</f>
@@ -4594,12 +4591,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B26" s="27" t="str">
         <f aca="false">IF(C13&gt;=1,"OK — omløpsmidlene dekker den kortsiktige gjelden","AVVIK: likviditetsgrad 1 er under 100 prosent — omløpsmidlene dekker ikke engang gjelden som forfaller i år")</f>
@@ -4608,7 +4605,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B27" s="27" t="str">
         <f aca="false">IF(ABS(C16-(1-C15)/C15)&lt;0.001,"OK — de to henger sammen","AVVIK: gjeldsgraden er regnet av noe annet enn egenkapitalandelen")</f>
@@ -4617,37 +4614,37 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4664,17 +4661,17 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4719,33 +4716,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>600000</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4753,42 +4750,42 @@
         <v>47</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="D9" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="E9" s="23" t="s">
         <v>348</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">Nordlys!B34</f>
-        <v>2910000</v>
+        <v>2892650</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">B10-$B$7</f>
-        <v>2310000</v>
+        <v>2292650</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">Nordlys!B29</f>
-        <v>10200000</v>
+        <v>10182650</v>
       </c>
       <c r="C11" s="25" t="n">
         <f aca="false">B11-$B$7</f>
-        <v>9600000</v>
+        <v>9582650</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4797,27 +4794,27 @@
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">Nordlys!B27</f>
-        <v>1000000</v>
+        <v>982650</v>
       </c>
       <c r="C12" s="25" t="n">
         <f aca="false">B12-$B$7</f>
-        <v>400000</v>
+        <v>382650</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">Nordlys!B28</f>
-        <v>6600000</v>
+        <v>6582650</v>
       </c>
       <c r="C13" s="25" t="n">
         <f aca="false">B13-$B$7</f>
-        <v>6000000</v>
+        <v>5982650</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4826,18 +4823,18 @@
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">B10/B11</f>
-        <v>0.285294117647059</v>
+        <v>0.284076345548556</v>
       </c>
       <c r="C14" s="28" t="n">
         <f aca="false">C10/C11</f>
-        <v>0.240625</v>
+        <v>0.239250103050826</v>
       </c>
       <c r="D14" s="36" t="n">
         <f aca="false">Nøkkeltall!D11</f>
         <v>0.362</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4846,18 +4843,18 @@
       </c>
       <c r="B15" s="30" t="n">
         <f aca="false">(B11-B10)/B10</f>
-        <v>2.50515463917526</v>
+        <v>2.52018045736608</v>
       </c>
       <c r="C15" s="30" t="n">
         <f aca="false">(C11-C10)/C10</f>
-        <v>3.15584415584416</v>
+        <v>3.17972651734892</v>
       </c>
       <c r="D15" s="37" t="n">
         <f aca="false">Nøkkeltall!D12</f>
         <v>5</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4866,11 +4863,11 @@
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">B13/Nordlys!B40</f>
-        <v>1.46993318485523</v>
+        <v>1.46606904231626</v>
       </c>
       <c r="C16" s="28" t="n">
         <f aca="false">C13/Nordlys!B40</f>
-        <v>1.33630289532294</v>
+        <v>1.33243875278396</v>
       </c>
       <c r="D16" s="36" t="n">
         <f aca="false">Nøkkeltall!D9</f>
@@ -4883,18 +4880,18 @@
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">(B13-Nordlys!B25)/Nordlys!B40</f>
-        <v>1.15812917594655</v>
+        <v>1.15426503340757</v>
       </c>
       <c r="C17" s="28" t="n">
         <f aca="false">(C13-Nordlys!B25)/Nordlys!B40</f>
-        <v>1.02449888641425</v>
+        <v>1.02063474387528</v>
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">Nøkkeltall!D10</f>
         <v>1</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4903,27 +4900,27 @@
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">Nordlys!B17/((Nordlys!B47+B10)/2)</f>
-        <v>0.486508585445626</v>
+        <v>0.479008749346107</v>
       </c>
       <c r="C18" s="28" t="n">
         <f aca="false">Nordlys!B17/((Nordlys!B47+C10)/2)</f>
-        <v>0.554520037278658</v>
+        <v>0.546243552103681</v>
       </c>
       <c r="D18" s="36" t="n">
         <f aca="false">Nøkkeltall!D8</f>
         <v>0.2</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B19" s="33" t="n">
         <f aca="false">$B$7/B12</f>
-        <v>0.6</v>
+        <v>0.610593802472905</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4933,7 +4930,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B22" s="27" t="str">
         <f aca="false">IF(C14&lt;B14,"AVVIK: egenkapitalandelen faller og gjeldsgraden stiger. Bedriften blir svakere på alt som betyr noe for banken","OK — utbyttet svekker ikke soliditeten")</f>
@@ -4942,12 +4939,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B24" s="27" t="str">
         <f aca="false">IF(C18&gt;B18,"AVVIK: egenkapitalrentabiliteten STIGER av utbyttet, samtidig som alt annet blir svakere. Et høyt tall kan være et faresignal","OK — egenkapitalrentabiliteten stiger ikke")</f>
@@ -4956,12 +4953,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B26" s="27" t="str">
         <f aca="false">IF(C12&gt;=0,"OK — bankinnskuddet dekker utbyttet, men se hva som blir igjen til lønn og merverdiavgift","AVVIK: bankinnskuddet dekker ikke utbyttet — pengene må hentes fra kassekreditten")</f>
@@ -4970,17 +4967,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B32" s="25" t="n">
         <f aca="false">Nordlys!B51</f>
@@ -4989,49 +4986,49 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B33" s="25" t="n">
         <f aca="false">Nordlys!B16</f>
-        <v>210000</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B34" s="32" t="n">
         <f aca="false">B33/B32</f>
-        <v>0.0285558879521349</v>
+        <v>0.0316154473755779</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>368</v>
-      </c>
-      <c r="B35" s="29" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B36" s="26" t="n">
         <f aca="false">B32*B35</f>
-        <v>441240</v>
+        <v>463302</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B37" s="26" t="n">
         <f aca="false">Nordlys!B14+Nordlys!B15-B36</f>
-        <v>958760</v>
+        <v>936698</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5040,10 +5037,10 @@
       </c>
       <c r="B38" s="28" t="n">
         <f aca="false">(B37+B36)/Nordlys!B49</f>
-        <v>0.142857142857143</v>
+        <v>0.142983712623164</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5052,31 +5049,31 @@
       </c>
       <c r="B39" s="28" t="n">
         <f aca="false">B37/Nordlys!B50</f>
-        <v>0.391970564186427</v>
+        <v>0.384313950745182</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B40" s="33" t="n">
         <f aca="false">(B38-B35)*100</f>
-        <v>8.28571428571429</v>
+        <v>7.99837126231639</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B41" s="28" t="n">
         <f aca="false">(Nordlys!B14+Nordlys!B15)/B32</f>
         <v>0.190372586347566</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5086,16 +5083,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B44" s="27" t="str">
-        <f aca="false">IF(B38&gt;B35,"OK — den lånte kapitalen tjener fortsatt mer enn den koster","AVVIK: lånerenta har passert totalkapitalrentabiliteten. Nå spiser gjelden egenkapitalen i stedet for å løfte den")</f>
+        <f aca="false">IF(B38&gt;B35,"OK — den lånte kapitalen tjener fortsatt mer enn den koster","AVVIK: gjeldsrenta har passert totalkapitalrentabiliteten. Nå spiser gjelden egenkapitalen i stedet for å løfte den")</f>
         <v>OK — den lånte kapitalen tjener fortsatt mer enn den koster</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B45" s="27" t="str">
         <f aca="false">IF(ABS(B38-Nøkkeltall!C7)&lt;0.0001,"OK — totalkapitalrentabiliteten er den samme uansett hva renta er. Det er nettopp derfor rentene legges tilbake i telleren","AVVIK: sjekk formlene — TKR skal ikke endre seg av renta alene")</f>
@@ -5104,32 +5101,32 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="23"/>
       <c r="B51" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="C51" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="D51" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="E51" s="23" t="s">
         <v>383</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B52" s="25" t="n">
         <f aca="false">Nordlys!$B$5</f>
@@ -5140,7 +5137,7 @@
         <v>22400000</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5248,7 +5245,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B60" s="24" t="n">
         <v>6000000</v>
@@ -5259,7 +5256,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5275,12 +5272,12 @@
         <v>940800</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B64" s="25" t="n">
         <f aca="false">B63/B54</f>
@@ -5291,12 +5288,12 @@
         <v>11760000</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B65" s="26" t="n">
         <f aca="false">B64*B58</f>
@@ -5309,7 +5306,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B66" s="26" t="n">
         <f aca="false">B64-B65</f>
@@ -5335,7 +5332,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B68" s="25" t="n">
         <f aca="false">B63-B67</f>
@@ -5348,7 +5345,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B69" s="32" t="n">
         <f aca="false">B68/B66</f>
@@ -5361,7 +5358,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B70" s="33" t="n">
         <f aca="false">(B54-B69)*100</f>
@@ -5372,17 +5369,17 @@
         <v>4.875</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="18" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B73" s="33" t="n">
         <f aca="false">B60/B65</f>
@@ -5395,7 +5392,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B74" s="28" t="n">
         <f aca="false">B67/B60</f>
@@ -5406,12 +5403,12 @@
         <v>0.0804631578947369</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="22" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B75" s="26" t="n">
         <f aca="false">B60+B66</f>
@@ -5422,12 +5419,12 @@
         <v>15144800</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B76" s="34" t="n">
         <f aca="false">ABS(B75-C75)</f>
@@ -5436,7 +5433,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B77" s="32" t="n">
         <f aca="false">B76/B75</f>
@@ -5450,7 +5447,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B80" s="27" t="str">
         <f aca="false">IF(B77&lt;0.05,"AVVIK: de to bedriftene koster praktisk talt det samme når gjelden regnes med. Prisantydningene alene sier deg altså ingenting","OK — de to koster ulikt også når gjelden regnes med")</f>
@@ -5459,12 +5456,12 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B82" s="27" t="str">
         <f aca="false">IF(AND(B68&gt;0,C68&gt;0),"OK — regnestykket henger sammen for begge bedriftene","AVVIK: negative rentekostnader betyr at egenkapitalrentabiliteten er satt for høyt i forhold til driftsmarginen")</f>
@@ -5473,7 +5470,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B83" s="27" t="str">
         <f aca="false">IF(AND(B54&gt;B69,C54&gt;C69),"OK — begge tjener mer på kapitalen enn den koster","AVVIK: minst én av bedriftene taper på gjelden sin")</f>
@@ -5482,7 +5479,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok04/OK04_Regnskapsanalyse_Regneark_Nokkeltall.xlsx
+++ b/pensum/ok04/OK04_Regnskapsanalyse_Regneark_Nokkeltall.xlsx
@@ -1463,7 +1463,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1618,6 +1618,10 @@
     </xf>
     <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1930,7 +1934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -2021,7 +2025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="24.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
@@ -2290,7 +2294,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+      <c s="39" r="A33" t="s">
         <v>69</v>
       </c>
       <c r="B33" s="20" t="s">
@@ -3350,8 +3354,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+    <row ht="27" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A33" t="s">
         <v>228</v>
       </c>
       <c r="B33" s="35" t="n">
@@ -3439,8 +3443,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
+    <row ht="27" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A45" t="s">
         <v>243</v>
       </c>
       <c r="B45" s="27" t="str">
@@ -3448,8 +3452,8 @@
         <v>OK — den lånte kapitalen tjener mer enn den koster, og differansen tilfaller eierne</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
+    <row ht="27" customHeight="true" r="46" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A46" t="s">
         <v>244</v>
       </c>
       <c r="B46" s="27" t="str">
@@ -3457,8 +3461,8 @@
         <v>OK — grad 2 er alltid lavest, fordi varelageret er trukket ut</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
+    <row ht="27" customHeight="true" r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A47" t="s">
         <v>245</v>
       </c>
       <c r="B47" s="27" t="str">
@@ -3466,8 +3470,8 @@
         <v>OK — gjeldsgraden og egenkapitalandelen sier det samme to ganger. Den ene er den andre snudd på hodet</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20" t="s">
+    <row ht="27" customHeight="true" r="48" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A48" t="s">
         <v>246</v>
       </c>
       <c r="B48" s="27" t="str">
@@ -3480,8 +3484,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20" t="s">
+    <row ht="52.5" customHeight="true" r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A50" t="s">
         <v>248</v>
       </c>
       <c r="B50" s="27" t="str">
@@ -4301,8 +4305,8 @@
         <v>OK — de to sidene er like store</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20" t="s">
+    <row ht="27" customHeight="true" r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A50" t="s">
         <v>243</v>
       </c>
       <c r="B50" s="27" t="str">
@@ -4594,8 +4598,8 @@
         <v>326</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+    <row ht="27" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A26" t="s">
         <v>327</v>
       </c>
       <c r="B26" s="27" t="str">
@@ -4603,8 +4607,8 @@
         <v>AVVIK: likviditetsgrad 1 er under 100 prosent — omløpsmidlene dekker ikke engang gjelden som forfaller i år</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+    <row ht="27" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A27" t="s">
         <v>328</v>
       </c>
       <c r="B27" s="27" t="str">
@@ -5002,8 +5006,8 @@
         <v>0.0316154473755779</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+    <row ht="27" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A35" t="s">
         <v>367</v>
       </c>
       <c r="B35" s="29" t="n">
@@ -5081,8 +5085,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20" t="s">
+    <row ht="27" customHeight="true" r="44" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A44" t="s">
         <v>376</v>
       </c>
       <c r="B44" s="27" t="str">
@@ -5109,7 +5113,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23"/>
       <c r="B51" s="23" t="s">
         <v>380</v>
